--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -28,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -49,8 +51,11 @@
       <family val="3"/>
       <sz val="6"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +65,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +86,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -91,6 +101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3719,6 +3730,527 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>element_id</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>通常属性または属性なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>火属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ice</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>氷</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>氷属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>雷</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>雷属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>holy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>聖</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>聖属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>闇</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>闇属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>毒属性</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>status_id</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>default_duration</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>stackable</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>毒</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>継続ダメージを与える状態異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>paralysis</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>麻痺</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>行動不能になる状態異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>burning</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>火傷</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>火傷による継続ダメージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>frostbite</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>凍傷</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>凍傷による継続ダメージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>眠って行動不能になる状態異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>confusion</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>混乱</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>行動が乱れる状態異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>blind</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>暗闇</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>命中や視界に影響する状態異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>幻覚</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>80</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>視覚や認識に影響する状態異常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>curse</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>呪い</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>呪い状態</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -4585,7 +4585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE33"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="29"/>
@@ -4637,112 +4637,137 @@
           <t>damage_mode</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>calculated_power</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>bonus_accuracy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bonus_crit_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ignore_defense_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fixed_damage_bonus</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>status_id</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>status_power</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>modifier_kind</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>stat_name</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>stat_flat</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>stat_percent</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>duration_type</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>duration_value</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>teleport_mode</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>teleport_min_range</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>teleport_max_range</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>warp_point_id</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>grant_item_id</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>grant_item_amount</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>grant_currency_amount</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>skill_id</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>recipe_id</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>identify_all</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>document_text</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>spawn_object_id</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>curse_status_pool</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>curse_status_power_overrides</t>
         </is>
@@ -4794,72 +4819,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="n"/>
       <c r="P2" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U2" s="1" t="n"/>
-      <c r="V2" s="1" t="n"/>
-      <c r="W2" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" s="1" t="n"/>
       <c r="Z2" s="1" t="n"/>
-      <c r="AA2" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB2" s="1" t="n"/>
-      <c r="AC2" s="1" t="n"/>
+      <c r="AA2" s="1" t="n"/>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD2" s="1" t="n"/>
       <c r="AE2" s="1" t="n"/>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="n"/>
+      <c r="AH2" s="1" t="n"/>
+      <c r="AI2" s="1" t="n"/>
+      <c r="AJ2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4907,72 +4957,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="n"/>
       <c r="P3" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="n"/>
+      <c r="R3" s="1" t="n"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U3" s="1" t="n"/>
-      <c r="V3" s="1" t="n"/>
-      <c r="W3" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X3" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" s="1" t="n"/>
       <c r="Z3" s="1" t="n"/>
-      <c r="AA3" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB3" s="1" t="n"/>
-      <c r="AC3" s="1" t="n"/>
+      <c r="AA3" s="1" t="n"/>
+      <c r="AB3" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD3" s="1" t="n"/>
       <c r="AE3" s="1" t="n"/>
+      <c r="AF3" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG3" s="1" t="n"/>
+      <c r="AH3" s="1" t="n"/>
+      <c r="AI3" s="1" t="n"/>
+      <c r="AJ3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5020,72 +5095,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="n"/>
       <c r="P4" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="n"/>
+      <c r="R4" s="1" t="n"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U4" s="1" t="n"/>
-      <c r="V4" s="1" t="n"/>
-      <c r="W4" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X4" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" s="1" t="n"/>
       <c r="Z4" s="1" t="n"/>
-      <c r="AA4" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB4" s="1" t="n"/>
-      <c r="AC4" s="1" t="n"/>
+      <c r="AA4" s="1" t="n"/>
+      <c r="AB4" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD4" s="1" t="n"/>
       <c r="AE4" s="1" t="n"/>
+      <c r="AF4" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG4" s="1" t="n"/>
+      <c r="AH4" s="1" t="n"/>
+      <c r="AI4" s="1" t="n"/>
+      <c r="AJ4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -5129,76 +5229,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
         <is>
           <t>poison</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="n"/>
+      <c r="R5" s="1" t="n"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P5" s="1" t="inlineStr">
+      <c r="U5" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q5" s="1" t="inlineStr">
+      <c r="V5" s="1" t="inlineStr">
         <is>
           <t>3600.0</t>
         </is>
       </c>
-      <c r="R5" s="1" t="inlineStr">
+      <c r="W5" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S5" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="1" t="inlineStr">
+      <c r="X5" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U5" s="1" t="n"/>
-      <c r="V5" s="1" t="n"/>
-      <c r="W5" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X5" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
-      <c r="AA5" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB5" s="1" t="n"/>
-      <c r="AC5" s="1" t="n"/>
+      <c r="AA5" s="1" t="n"/>
+      <c r="AB5" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD5" s="1" t="n"/>
       <c r="AE5" s="1" t="n"/>
+      <c r="AF5" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG5" s="1" t="n"/>
+      <c r="AH5" s="1" t="n"/>
+      <c r="AI5" s="1" t="n"/>
+      <c r="AJ5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -5242,76 +5367,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
         <is>
           <t>paralysis</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="n"/>
+      <c r="R6" s="1" t="n"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P6" s="1" t="inlineStr">
+      <c r="U6" s="1" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q6" s="1" t="inlineStr">
+      <c r="V6" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R6" s="1" t="inlineStr">
+      <c r="W6" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="1" t="inlineStr">
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U6" s="1" t="n"/>
-      <c r="V6" s="1" t="n"/>
-      <c r="W6" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X6" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
-      <c r="AA6" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB6" s="1" t="n"/>
-      <c r="AC6" s="1" t="n"/>
+      <c r="AA6" s="1" t="n"/>
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD6" s="1" t="n"/>
       <c r="AE6" s="1" t="n"/>
+      <c r="AF6" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG6" s="1" t="n"/>
+      <c r="AH6" s="1" t="n"/>
+      <c r="AI6" s="1" t="n"/>
+      <c r="AJ6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -5355,76 +5505,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
         <is>
           <t>poison</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="n"/>
-      <c r="M7" s="1" t="n"/>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="n"/>
+      <c r="R7" s="1" t="n"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="U7" s="1" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="V7" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="W7" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="X7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U7" s="1" t="n"/>
-      <c r="V7" s="1" t="n"/>
-      <c r="W7" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" s="1" t="n"/>
       <c r="Z7" s="1" t="n"/>
-      <c r="AA7" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB7" s="1" t="n"/>
-      <c r="AC7" s="1" t="n"/>
+      <c r="AA7" s="1" t="n"/>
+      <c r="AB7" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD7" s="1" t="n"/>
       <c r="AE7" s="1" t="n"/>
+      <c r="AF7" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG7" s="1" t="n"/>
+      <c r="AH7" s="1" t="n"/>
+      <c r="AI7" s="1" t="n"/>
+      <c r="AJ7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -5468,80 +5643,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J8" s="1" t="n"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n"/>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="R8" s="1" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="1" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="P8" s="1" t="inlineStr">
+      <c r="U8" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q8" s="1" t="inlineStr">
+      <c r="V8" s="1" t="inlineStr">
         <is>
           <t>7200.0</t>
         </is>
       </c>
-      <c r="R8" s="1" t="inlineStr">
+      <c r="W8" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S8" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="1" t="inlineStr">
+      <c r="X8" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U8" s="1" t="n"/>
-      <c r="V8" s="1" t="n"/>
-      <c r="W8" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X8" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" s="1" t="n"/>
       <c r="Z8" s="1" t="n"/>
-      <c r="AA8" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB8" s="1" t="n"/>
-      <c r="AC8" s="1" t="n"/>
+      <c r="AA8" s="1" t="n"/>
+      <c r="AB8" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD8" s="1" t="n"/>
       <c r="AE8" s="1" t="n"/>
+      <c r="AF8" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG8" s="1" t="n"/>
+      <c r="AH8" s="1" t="n"/>
+      <c r="AI8" s="1" t="n"/>
+      <c r="AJ8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -5585,72 +5785,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J9" s="1" t="n"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="n"/>
-      <c r="M9" s="1" t="n"/>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="n"/>
       <c r="P9" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="n"/>
+      <c r="R9" s="1" t="n"/>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U9" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q9" s="1" t="inlineStr">
+      <c r="V9" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R9" s="1" t="inlineStr">
+      <c r="W9" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S9" s="1" t="inlineStr">
+      <c r="X9" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T9" s="1" t="inlineStr">
+      <c r="Y9" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U9" s="1" t="n"/>
-      <c r="V9" s="1" t="n"/>
-      <c r="W9" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X9" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" s="1" t="n"/>
       <c r="Z9" s="1" t="n"/>
-      <c r="AA9" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB9" s="1" t="n"/>
-      <c r="AC9" s="1" t="n"/>
+      <c r="AA9" s="1" t="n"/>
+      <c r="AB9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD9" s="1" t="n"/>
       <c r="AE9" s="1" t="n"/>
+      <c r="AF9" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG9" s="1" t="n"/>
+      <c r="AH9" s="1" t="n"/>
+      <c r="AI9" s="1" t="n"/>
+      <c r="AJ9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -5694,76 +5919,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
         <is>
           <t>burning</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="P10" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L10" s="1" t="n"/>
-      <c r="M10" s="1" t="n"/>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
+      <c r="Q10" s="1" t="n"/>
+      <c r="R10" s="1" t="n"/>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P10" s="1" t="inlineStr">
+      <c r="U10" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q10" s="1" t="inlineStr">
+      <c r="V10" s="1" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="R10" s="1" t="inlineStr">
+      <c r="W10" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S10" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="1" t="inlineStr">
+      <c r="X10" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U10" s="1" t="n"/>
-      <c r="V10" s="1" t="n"/>
-      <c r="W10" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X10" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" s="1" t="n"/>
       <c r="Z10" s="1" t="n"/>
-      <c r="AA10" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB10" s="1" t="n"/>
-      <c r="AC10" s="1" t="n"/>
+      <c r="AA10" s="1" t="n"/>
+      <c r="AB10" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD10" s="1" t="n"/>
       <c r="AE10" s="1" t="n"/>
+      <c r="AF10" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG10" s="1" t="n"/>
+      <c r="AH10" s="1" t="n"/>
+      <c r="AI10" s="1" t="n"/>
+      <c r="AJ10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -5807,76 +6057,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>frostbite</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L11" s="1" t="n"/>
-      <c r="M11" s="1" t="n"/>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="Q11" s="1" t="n"/>
+      <c r="R11" s="1" t="n"/>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
+      <c r="V11" s="1" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="W11" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="1" t="inlineStr">
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U11" s="1" t="n"/>
-      <c r="V11" s="1" t="n"/>
-      <c r="W11" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X11" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" s="1" t="n"/>
       <c r="Z11" s="1" t="n"/>
-      <c r="AA11" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB11" s="1" t="n"/>
-      <c r="AC11" s="1" t="n"/>
+      <c r="AA11" s="1" t="n"/>
+      <c r="AB11" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD11" s="1" t="n"/>
       <c r="AE11" s="1" t="n"/>
+      <c r="AF11" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG11" s="1" t="n"/>
+      <c r="AH11" s="1" t="n"/>
+      <c r="AI11" s="1" t="n"/>
+      <c r="AJ11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -5920,76 +6195,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="n"/>
-      <c r="M12" s="1" t="n"/>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="n"/>
+      <c r="R12" s="1" t="n"/>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr">
+      <c r="U12" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
+      <c r="V12" s="1" t="inlineStr">
         <is>
           <t>5000.0</t>
         </is>
       </c>
-      <c r="R12" s="1" t="inlineStr">
+      <c r="W12" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S12" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="1" t="inlineStr">
+      <c r="X12" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U12" s="1" t="n"/>
-      <c r="V12" s="1" t="n"/>
-      <c r="W12" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X12" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y12" s="1" t="n"/>
       <c r="Z12" s="1" t="n"/>
-      <c r="AA12" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB12" s="1" t="n"/>
-      <c r="AC12" s="1" t="n"/>
+      <c r="AA12" s="1" t="n"/>
+      <c r="AB12" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC12" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD12" s="1" t="n"/>
       <c r="AE12" s="1" t="n"/>
+      <c r="AF12" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG12" s="1" t="n"/>
+      <c r="AH12" s="1" t="n"/>
+      <c r="AI12" s="1" t="n"/>
+      <c r="AJ12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -6033,76 +6333,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>confusion</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="n"/>
-      <c r="M13" s="1" t="n"/>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="n"/>
+      <c r="R13" s="1" t="n"/>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="W13" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="1" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U13" s="1" t="n"/>
-      <c r="V13" s="1" t="n"/>
-      <c r="W13" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X13" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" s="1" t="n"/>
       <c r="Z13" s="1" t="n"/>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="n"/>
-      <c r="AC13" s="1" t="n"/>
+      <c r="AA13" s="1" t="n"/>
+      <c r="AB13" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD13" s="1" t="n"/>
       <c r="AE13" s="1" t="n"/>
+      <c r="AF13" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG13" s="1" t="n"/>
+      <c r="AH13" s="1" t="n"/>
+      <c r="AI13" s="1" t="n"/>
+      <c r="AJ13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -6146,80 +6471,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J14" s="1" t="n"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="n"/>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>defense</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="1" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="U14" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q14" s="1" t="inlineStr">
+      <c r="V14" s="1" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="R14" s="1" t="inlineStr">
+      <c r="W14" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S14" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="1" t="inlineStr">
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y14" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U14" s="1" t="n"/>
-      <c r="V14" s="1" t="n"/>
-      <c r="W14" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X14" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y14" s="1" t="n"/>
       <c r="Z14" s="1" t="n"/>
-      <c r="AA14" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB14" s="1" t="n"/>
-      <c r="AC14" s="1" t="n"/>
+      <c r="AA14" s="1" t="n"/>
+      <c r="AB14" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD14" s="1" t="n"/>
       <c r="AE14" s="1" t="n"/>
+      <c r="AF14" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG14" s="1" t="n"/>
+      <c r="AH14" s="1" t="n"/>
+      <c r="AI14" s="1" t="n"/>
+      <c r="AJ14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -6263,80 +6613,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J15" s="1" t="n"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="n"/>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" s="1" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="U15" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
+      <c r="V15" s="1" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="W15" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S15" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="1" t="inlineStr">
+      <c r="X15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U15" s="1" t="n"/>
-      <c r="V15" s="1" t="n"/>
-      <c r="W15" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X15" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y15" s="1" t="n"/>
       <c r="Z15" s="1" t="n"/>
-      <c r="AA15" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB15" s="1" t="n"/>
-      <c r="AC15" s="1" t="n"/>
+      <c r="AA15" s="1" t="n"/>
+      <c r="AB15" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD15" s="1" t="n"/>
       <c r="AE15" s="1" t="n"/>
+      <c r="AF15" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG15" s="1" t="n"/>
+      <c r="AH15" s="1" t="n"/>
+      <c r="AI15" s="1" t="n"/>
+      <c r="AJ15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -6380,80 +6755,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J16" s="1" t="n"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="n"/>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" s="1" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="R16" s="1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="S16" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="T16" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr">
+      <c r="U16" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q16" s="1" t="inlineStr">
+      <c r="V16" s="1" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="R16" s="1" t="inlineStr">
+      <c r="W16" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="1" t="inlineStr">
+      <c r="X16" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U16" s="1" t="n"/>
-      <c r="V16" s="1" t="n"/>
-      <c r="W16" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X16" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y16" s="1" t="n"/>
       <c r="Z16" s="1" t="n"/>
-      <c r="AA16" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB16" s="1" t="n"/>
-      <c r="AC16" s="1" t="n"/>
+      <c r="AA16" s="1" t="n"/>
+      <c r="AB16" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD16" s="1" t="n"/>
       <c r="AE16" s="1" t="n"/>
+      <c r="AF16" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG16" s="1" t="n"/>
+      <c r="AH16" s="1" t="n"/>
+      <c r="AI16" s="1" t="n"/>
+      <c r="AJ16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -6497,80 +6897,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J17" s="1" t="n"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="n"/>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="R17" s="1" t="inlineStr">
         <is>
           <t>evasion</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="S17" s="1" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
+      <c r="T17" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P17" s="1" t="inlineStr">
+      <c r="U17" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q17" s="1" t="inlineStr">
+      <c r="V17" s="1" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="R17" s="1" t="inlineStr">
+      <c r="W17" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S17" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="1" t="inlineStr">
+      <c r="X17" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U17" s="1" t="n"/>
-      <c r="V17" s="1" t="n"/>
-      <c r="W17" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X17" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y17" s="1" t="n"/>
       <c r="Z17" s="1" t="n"/>
-      <c r="AA17" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB17" s="1" t="n"/>
-      <c r="AC17" s="1" t="n"/>
+      <c r="AA17" s="1" t="n"/>
+      <c r="AB17" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD17" s="1" t="n"/>
       <c r="AE17" s="1" t="n"/>
+      <c r="AF17" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG17" s="1" t="n"/>
+      <c r="AH17" s="1" t="n"/>
+      <c r="AI17" s="1" t="n"/>
+      <c r="AJ17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -6614,80 +7039,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J18" s="1" t="n"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="n"/>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" s="1" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="R18" s="1" t="inlineStr">
         <is>
           <t>crit_rate</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="S18" s="1" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O18" s="1" t="inlineStr">
+      <c r="T18" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P18" s="1" t="inlineStr">
+      <c r="U18" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q18" s="1" t="inlineStr">
+      <c r="V18" s="1" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="R18" s="1" t="inlineStr">
+      <c r="W18" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S18" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="1" t="inlineStr">
+      <c r="X18" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y18" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U18" s="1" t="n"/>
-      <c r="V18" s="1" t="n"/>
-      <c r="W18" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X18" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y18" s="1" t="n"/>
       <c r="Z18" s="1" t="n"/>
-      <c r="AA18" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB18" s="1" t="n"/>
-      <c r="AC18" s="1" t="n"/>
+      <c r="AA18" s="1" t="n"/>
+      <c r="AB18" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD18" s="1" t="n"/>
       <c r="AE18" s="1" t="n"/>
+      <c r="AF18" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG18" s="1" t="n"/>
+      <c r="AH18" s="1" t="n"/>
+      <c r="AI18" s="1" t="n"/>
+      <c r="AJ18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -6731,72 +7181,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J19" s="1" t="n"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="n"/>
-      <c r="M19" s="1" t="n"/>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="n"/>
       <c r="P19" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="n"/>
+      <c r="R19" s="1" t="n"/>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U19" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q19" s="1" t="inlineStr">
+      <c r="V19" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R19" s="1" t="inlineStr">
+      <c r="W19" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S19" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="1" t="inlineStr">
+      <c r="X19" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U19" s="1" t="n"/>
-      <c r="V19" s="1" t="n"/>
-      <c r="W19" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X19" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y19" s="1" t="n"/>
       <c r="Z19" s="1" t="n"/>
-      <c r="AA19" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB19" s="1" t="n"/>
-      <c r="AC19" s="1" t="n"/>
+      <c r="AA19" s="1" t="n"/>
+      <c r="AB19" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC19" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD19" s="1" t="n"/>
       <c r="AE19" s="1" t="n"/>
+      <c r="AF19" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG19" s="1" t="n"/>
+      <c r="AH19" s="1" t="n"/>
+      <c r="AI19" s="1" t="n"/>
+      <c r="AJ19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -6840,80 +7315,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J20" s="1" t="n"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="n"/>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>defense</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="1" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="P20" s="1" t="inlineStr">
+      <c r="U20" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q20" s="1" t="inlineStr">
+      <c r="V20" s="1" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="R20" s="1" t="inlineStr">
+      <c r="W20" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S20" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="1" t="inlineStr">
+      <c r="X20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y20" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U20" s="1" t="n"/>
-      <c r="V20" s="1" t="n"/>
-      <c r="W20" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X20" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y20" s="1" t="n"/>
       <c r="Z20" s="1" t="n"/>
-      <c r="AA20" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB20" s="1" t="n"/>
-      <c r="AC20" s="1" t="n"/>
+      <c r="AA20" s="1" t="n"/>
+      <c r="AB20" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD20" s="1" t="n"/>
       <c r="AE20" s="1" t="n"/>
+      <c r="AF20" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG20" s="1" t="n"/>
+      <c r="AH20" s="1" t="n"/>
+      <c r="AI20" s="1" t="n"/>
+      <c r="AJ20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -6957,80 +7457,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J21" s="1" t="n"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="n"/>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="R21" s="1" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="1" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="P21" s="1" t="inlineStr">
+      <c r="U21" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q21" s="1" t="inlineStr">
+      <c r="V21" s="1" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="R21" s="1" t="inlineStr">
+      <c r="W21" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S21" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="1" t="inlineStr">
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y21" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U21" s="1" t="n"/>
-      <c r="V21" s="1" t="n"/>
-      <c r="W21" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X21" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y21" s="1" t="n"/>
       <c r="Z21" s="1" t="n"/>
-      <c r="AA21" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB21" s="1" t="n"/>
-      <c r="AC21" s="1" t="n"/>
+      <c r="AA21" s="1" t="n"/>
+      <c r="AB21" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD21" s="1" t="n"/>
       <c r="AE21" s="1" t="n"/>
+      <c r="AF21" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG21" s="1" t="n"/>
+      <c r="AH21" s="1" t="n"/>
+      <c r="AI21" s="1" t="n"/>
+      <c r="AJ21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -7074,80 +7599,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J22" s="1" t="n"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="n"/>
+      <c r="P22" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" s="1" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="S22" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="T22" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr">
+      <c r="U22" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q22" s="1" t="inlineStr">
+      <c r="V22" s="1" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="R22" s="1" t="inlineStr">
+      <c r="W22" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S22" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="1" t="inlineStr">
+      <c r="X22" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y22" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U22" s="1" t="n"/>
-      <c r="V22" s="1" t="n"/>
-      <c r="W22" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X22" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y22" s="1" t="n"/>
       <c r="Z22" s="1" t="n"/>
-      <c r="AA22" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB22" s="1" t="n"/>
-      <c r="AC22" s="1" t="n"/>
+      <c r="AA22" s="1" t="n"/>
+      <c r="AB22" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC22" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD22" s="1" t="n"/>
       <c r="AE22" s="1" t="n"/>
+      <c r="AF22" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG22" s="1" t="n"/>
+      <c r="AH22" s="1" t="n"/>
+      <c r="AI22" s="1" t="n"/>
+      <c r="AJ22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -7191,80 +7741,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="n"/>
+      <c r="P23" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q23" s="1" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>evasion</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="S23" s="1" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="T23" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P23" s="1" t="inlineStr">
+      <c r="U23" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q23" s="1" t="inlineStr">
+      <c r="V23" s="1" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr">
+      <c r="W23" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S23" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="1" t="inlineStr">
+      <c r="X23" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y23" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U23" s="1" t="n"/>
-      <c r="V23" s="1" t="n"/>
-      <c r="W23" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X23" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y23" s="1" t="n"/>
       <c r="Z23" s="1" t="n"/>
-      <c r="AA23" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB23" s="1" t="n"/>
-      <c r="AC23" s="1" t="n"/>
+      <c r="AA23" s="1" t="n"/>
+      <c r="AB23" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC23" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD23" s="1" t="n"/>
       <c r="AE23" s="1" t="n"/>
+      <c r="AF23" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG23" s="1" t="n"/>
+      <c r="AH23" s="1" t="n"/>
+      <c r="AI23" s="1" t="n"/>
+      <c r="AJ23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -7308,80 +7883,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="n"/>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="M24" s="1" t="inlineStr">
+      <c r="R24" s="1" t="inlineStr">
         <is>
           <t>crit_rate</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="S24" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="O24" s="1" t="inlineStr">
+      <c r="T24" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P24" s="1" t="inlineStr">
+      <c r="U24" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q24" s="1" t="inlineStr">
+      <c r="V24" s="1" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="R24" s="1" t="inlineStr">
+      <c r="W24" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S24" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="1" t="inlineStr">
+      <c r="X24" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y24" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U24" s="1" t="n"/>
-      <c r="V24" s="1" t="n"/>
-      <c r="W24" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X24" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y24" s="1" t="n"/>
       <c r="Z24" s="1" t="n"/>
-      <c r="AA24" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB24" s="1" t="n"/>
-      <c r="AC24" s="1" t="n"/>
+      <c r="AA24" s="1" t="n"/>
+      <c r="AB24" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD24" s="1" t="n"/>
       <c r="AE24" s="1" t="n"/>
+      <c r="AF24" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG24" s="1" t="n"/>
+      <c r="AH24" s="1" t="n"/>
+      <c r="AI24" s="1" t="n"/>
+      <c r="AJ24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7425,76 +8025,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J25" s="1" t="n"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="1" t="n"/>
-      <c r="M25" s="1" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="n"/>
+      <c r="P25" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q25" s="1" t="n"/>
+      <c r="R25" s="1" t="inlineStr">
         <is>
           <t>max_hp</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="S25" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P25" s="1" t="inlineStr">
+      <c r="U25" s="1" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q25" s="1" t="inlineStr">
+      <c r="V25" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R25" s="1" t="inlineStr">
+      <c r="W25" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S25" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="1" t="inlineStr">
+      <c r="X25" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y25" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U25" s="1" t="n"/>
-      <c r="V25" s="1" t="n"/>
-      <c r="W25" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X25" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y25" s="1" t="n"/>
       <c r="Z25" s="1" t="n"/>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB25" s="1" t="n"/>
-      <c r="AC25" s="1" t="n"/>
+      <c r="AA25" s="1" t="n"/>
+      <c r="AB25" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD25" s="1" t="n"/>
       <c r="AE25" s="1" t="n"/>
+      <c r="AF25" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG25" s="1" t="n"/>
+      <c r="AH25" s="1" t="n"/>
+      <c r="AI25" s="1" t="n"/>
+      <c r="AJ25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -7538,72 +8163,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J26" s="1" t="n"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="n"/>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O26" s="1" t="n"/>
       <c r="P26" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q26" s="1" t="n"/>
+      <c r="R26" s="1" t="n"/>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U26" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q26" s="1" t="inlineStr">
+      <c r="V26" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R26" s="1" t="inlineStr">
+      <c r="W26" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S26" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="1" t="inlineStr">
+      <c r="X26" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y26" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U26" s="1" t="n"/>
-      <c r="V26" s="1" t="n"/>
-      <c r="W26" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X26" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y26" s="1" t="n"/>
       <c r="Z26" s="1" t="n"/>
-      <c r="AA26" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB26" s="1" t="n"/>
-      <c r="AC26" s="1" t="n"/>
+      <c r="AA26" s="1" t="n"/>
+      <c r="AB26" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD26" s="1" t="n"/>
       <c r="AE26" s="1" t="n"/>
+      <c r="AF26" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG26" s="1" t="n"/>
+      <c r="AH26" s="1" t="n"/>
+      <c r="AI26" s="1" t="n"/>
+      <c r="AJ26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -7647,72 +8297,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J27" s="1" t="n"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="n"/>
       <c r="P27" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="n"/>
+      <c r="R27" s="1" t="n"/>
+      <c r="S27" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U27" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q27" s="1" t="inlineStr">
+      <c r="V27" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R27" s="1" t="inlineStr">
+      <c r="W27" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S27" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="1" t="inlineStr">
+      <c r="X27" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y27" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U27" s="1" t="n"/>
-      <c r="V27" s="1" t="n"/>
-      <c r="W27" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X27" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y27" s="1" t="n"/>
       <c r="Z27" s="1" t="n"/>
-      <c r="AA27" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB27" s="1" t="n"/>
-      <c r="AC27" s="1" t="n"/>
+      <c r="AA27" s="1" t="n"/>
+      <c r="AB27" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD27" s="1" t="n"/>
       <c r="AE27" s="1" t="n"/>
+      <c r="AF27" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG27" s="1" t="n"/>
+      <c r="AH27" s="1" t="n"/>
+      <c r="AI27" s="1" t="n"/>
+      <c r="AJ27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -7756,76 +8431,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
         <is>
           <t>blind</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="n"/>
-      <c r="M28" s="1" t="n"/>
-      <c r="N28" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" s="1" t="n"/>
+      <c r="R28" s="1" t="n"/>
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr">
+      <c r="U28" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q28" s="1" t="inlineStr">
+      <c r="V28" s="1" t="inlineStr">
         <is>
           <t>5000.0</t>
         </is>
       </c>
-      <c r="R28" s="1" t="inlineStr">
+      <c r="W28" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S28" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="1" t="inlineStr">
+      <c r="X28" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y28" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U28" s="1" t="n"/>
-      <c r="V28" s="1" t="n"/>
-      <c r="W28" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X28" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y28" s="1" t="n"/>
       <c r="Z28" s="1" t="n"/>
-      <c r="AA28" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB28" s="1" t="n"/>
-      <c r="AC28" s="1" t="n"/>
+      <c r="AA28" s="1" t="n"/>
+      <c r="AB28" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD28" s="1" t="n"/>
       <c r="AE28" s="1" t="n"/>
+      <c r="AF28" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG28" s="1" t="n"/>
+      <c r="AH28" s="1" t="n"/>
+      <c r="AI28" s="1" t="n"/>
+      <c r="AJ28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -7869,76 +8569,101 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
         <is>
           <t>hallucination</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="n"/>
-      <c r="M29" s="1" t="n"/>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
+      <c r="P29" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" s="1" t="n"/>
+      <c r="R29" s="1" t="n"/>
+      <c r="S29" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P29" s="1" t="inlineStr">
+      <c r="U29" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q29" s="1" t="inlineStr">
+      <c r="V29" s="1" t="inlineStr">
         <is>
           <t>5000.0</t>
         </is>
       </c>
-      <c r="R29" s="1" t="inlineStr">
+      <c r="W29" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S29" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="1" t="inlineStr">
+      <c r="X29" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y29" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U29" s="1" t="n"/>
-      <c r="V29" s="1" t="n"/>
-      <c r="W29" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X29" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y29" s="1" t="n"/>
       <c r="Z29" s="1" t="n"/>
-      <c r="AA29" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB29" s="1" t="n"/>
-      <c r="AC29" s="1" t="n"/>
+      <c r="AA29" s="1" t="n"/>
+      <c r="AB29" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD29" s="1" t="n"/>
       <c r="AE29" s="1" t="n"/>
+      <c r="AF29" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG29" s="1" t="n"/>
+      <c r="AH29" s="1" t="n"/>
+      <c r="AI29" s="1" t="n"/>
+      <c r="AJ29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -7982,80 +8707,105 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
         <is>
           <t>curse</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="n"/>
-      <c r="M30" s="1" t="n"/>
-      <c r="N30" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="n"/>
+      <c r="R30" s="1" t="n"/>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P30" s="1" t="inlineStr">
+      <c r="U30" s="1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="Q30" s="1" t="inlineStr">
+      <c r="V30" s="1" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="R30" s="1" t="inlineStr">
+      <c r="W30" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S30" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="1" t="inlineStr">
+      <c r="X30" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y30" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U30" s="1" t="n"/>
-      <c r="V30" s="1" t="n"/>
-      <c r="W30" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X30" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y30" s="1" t="n"/>
       <c r="Z30" s="1" t="n"/>
-      <c r="AA30" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB30" s="1" t="n"/>
-      <c r="AC30" s="1" t="n"/>
-      <c r="AD30" s="1" t="inlineStr">
+      <c r="AA30" s="1" t="n"/>
+      <c r="AB30" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD30" s="1" t="n"/>
+      <c r="AE30" s="1" t="n"/>
+      <c r="AF30" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG30" s="1" t="n"/>
+      <c r="AH30" s="1" t="n"/>
+      <c r="AI30" s="1" t="inlineStr">
         <is>
           <t>poison|blind|confusion|burning|hallucination|frostbite|paralysis</t>
         </is>
       </c>
-      <c r="AE30" s="1" t="inlineStr">
+      <c r="AJ30" s="1" t="inlineStr">
         <is>
           <t>2|0|0|2</t>
         </is>
@@ -8107,72 +8857,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J31" s="1" t="n"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="n"/>
       <c r="P31" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" s="1" t="n"/>
+      <c r="R31" s="1" t="n"/>
+      <c r="S31" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U31" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q31" s="1" t="inlineStr">
+      <c r="V31" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R31" s="1" t="inlineStr">
+      <c r="W31" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="1" t="inlineStr">
+      <c r="X31" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y31" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U31" s="1" t="n"/>
-      <c r="V31" s="1" t="n"/>
-      <c r="W31" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X31" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y31" s="1" t="n"/>
       <c r="Z31" s="1" t="n"/>
-      <c r="AA31" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB31" s="1" t="n"/>
-      <c r="AC31" s="1" t="n"/>
+      <c r="AA31" s="1" t="n"/>
+      <c r="AB31" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD31" s="1" t="n"/>
       <c r="AE31" s="1" t="n"/>
+      <c r="AF31" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG31" s="1" t="n"/>
+      <c r="AH31" s="1" t="n"/>
+      <c r="AI31" s="1" t="n"/>
+      <c r="AJ31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -8220,72 +8995,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J32" s="1" t="n"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="n"/>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="n"/>
       <c r="P32" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" s="1" t="n"/>
+      <c r="R32" s="1" t="n"/>
+      <c r="S32" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U32" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q32" s="1" t="inlineStr">
+      <c r="V32" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
+      <c r="W32" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S32" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="1" t="inlineStr">
+      <c r="X32" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y32" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U32" s="1" t="n"/>
-      <c r="V32" s="1" t="n"/>
-      <c r="W32" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X32" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y32" s="1" t="n"/>
       <c r="Z32" s="1" t="n"/>
-      <c r="AA32" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB32" s="1" t="n"/>
-      <c r="AC32" s="1" t="n"/>
+      <c r="AA32" s="1" t="n"/>
+      <c r="AB32" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD32" s="1" t="n"/>
       <c r="AE32" s="1" t="n"/>
+      <c r="AF32" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG32" s="1" t="n"/>
+      <c r="AH32" s="1" t="n"/>
+      <c r="AI32" s="1" t="n"/>
+      <c r="AJ32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -8333,72 +9133,97 @@
           <t>direct</t>
         </is>
       </c>
-      <c r="J33" s="1" t="n"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="n"/>
-      <c r="M33" s="1" t="n"/>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="n"/>
       <c r="P33" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" s="1" t="n"/>
+      <c r="R33" s="1" t="n"/>
+      <c r="S33" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T33" s="1" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U33" s="1" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q33" s="1" t="inlineStr">
+      <c r="V33" s="1" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R33" s="1" t="inlineStr">
+      <c r="W33" s="1" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S33" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" s="1" t="inlineStr">
+      <c r="X33" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y33" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="U33" s="1" t="n"/>
-      <c r="V33" s="1" t="n"/>
-      <c r="W33" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X33" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y33" s="1" t="n"/>
       <c r="Z33" s="1" t="n"/>
-      <c r="AA33" s="1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AB33" s="1" t="n"/>
-      <c r="AC33" s="1" t="n"/>
+      <c r="AA33" s="1" t="n"/>
+      <c r="AB33" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AD33" s="1" t="n"/>
       <c r="AE33" s="1" t="n"/>
+      <c r="AF33" s="1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG33" s="1" t="n"/>
+      <c r="AH33" s="1" t="n"/>
+      <c r="AI33" s="1" t="n"/>
+      <c r="AJ33" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -2,33 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="R56b08c0e5e28461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="R60102ce5d0414b72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R4908e9e9f82348eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="R8a769a27f927451e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R3f67e7fe41f54801"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="Rc080280500a749ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Rb04775bb84a14a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="R47e9207a0a964d90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="Rff24bb477bcd471c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="Rbc7d7f6a589545c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="R79c4ab08764d4132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R1db2535f737245f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="R5d6b8e51365842a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="R8e1df15929434cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="R609f55c4a7d5410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="R02fd733520834ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="Rc74285fb11734cb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="Rfa6b2c0e36644232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="R01406753d752433f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="Rb086b9e299c54950"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="Rd4f597426c4b42ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="Rc7dbd5d14a754b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="R06b32de345b94bd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R511403d3ae564df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R31e1f4b3e6414470"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="R2e6910303696467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="Raa8536a2288d4924"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="R6edce7e78d424ff5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="R0d8be91373564df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R77ebe784716b4a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="R9e4f911465d849c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="Rc9eea8a79bbb4e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="R6f15b4fbec544116"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="R6cb51b4d5c45487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="Rdb120f8fd83d4e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="Ref33b68c8e0b45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="R58268b18c4a94aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="R56db515f22b94b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R92df3f27947f4eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="Rebcd38860e9240bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="Rc707ebb803ef499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="Rb430a0353d9f48a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="Rffe5d355b3b04da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="R5052055502b748c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="R2bc1d8c668ca446e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="R07586b0588b1469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="Ra4dae40796f946aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="Rc6a597f7438c491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="Rdf4eef625bcd4015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="R9cd7699d064c42c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R3a50ab2c83ae49f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="Rf7954a2d7ef4449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="Reda70d7c572743d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="Rea65e3a3b46a435a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="Rbb45f35494ac49d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="Re5b033fa9dfc4835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R272822e3f346489a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +67,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -81,6 +84,16 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -89,7 +102,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1"/>
     <x:xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
@@ -124,6 +137,10 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="標準" xfId="0"/>
@@ -18418,74 +18435,106 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" customWidth="1"/>
-    <x:col min="2" max="2" width="13" customWidth="1"/>
-    <x:col min="3" max="4" width="10" customWidth="1"/>
-    <x:col min="5" max="5" width="17" customWidth="1"/>
-    <x:col min="6" max="6" width="22" customWidth="1"/>
-    <x:col min="7" max="7" width="10" customWidth="1"/>
-    <x:col min="8" max="8" width="14" customWidth="1"/>
-    <x:col min="9" max="14" width="10" customWidth="1"/>
-    <x:col min="15" max="15" width="11" customWidth="1"/>
-    <x:col min="16" max="16" width="13" customWidth="1"/>
-    <x:col min="17" max="18" width="10" customWidth="1"/>
-    <x:col min="19" max="19" width="24" customWidth="1"/>
-    <x:col min="20" max="20" width="28" customWidth="1"/>
-    <x:col min="21" max="21" width="21" customWidth="1"/>
-    <x:col min="22" max="24" width="10" customWidth="1"/>
-    <x:col min="25" max="25" width="11" customWidth="1"/>
-    <x:col min="26" max="26" width="14" customWidth="1"/>
-    <x:col min="27" max="29" width="10" customWidth="1"/>
-    <x:col min="30" max="30" width="11" customWidth="1"/>
-    <x:col min="31" max="31" width="15" customWidth="1"/>
-    <x:col min="32" max="32" width="10" customWidth="1"/>
-    <x:col min="33" max="33" width="13" customWidth="1"/>
-    <x:col min="34" max="34" width="10" customWidth="1"/>
-    <x:col min="35" max="35" width="11" customWidth="1"/>
-    <x:col min="36" max="39" width="10" customWidth="1"/>
-    <x:col min="40" max="40" width="13" customWidth="1"/>
-    <x:col min="41" max="42" width="10" customWidth="1"/>
-    <x:col min="43" max="43" width="17" customWidth="1"/>
-    <x:col min="44" max="44" width="16" customWidth="1"/>
-    <x:col min="45" max="45" width="20" customWidth="1"/>
-    <x:col min="46" max="46" width="21" customWidth="1"/>
-    <x:col min="47" max="47" width="20" customWidth="1"/>
-    <x:col min="48" max="49" width="15" customWidth="1"/>
-    <x:col min="50" max="51" width="16" customWidth="1"/>
-    <x:col min="52" max="52" width="15" customWidth="1"/>
-    <x:col min="53" max="56" width="22" customWidth="1"/>
-    <x:col min="57" max="58" width="25" customWidth="1"/>
-    <x:col min="59" max="59" width="30" customWidth="1"/>
-    <x:col min="60" max="60" width="29" customWidth="1"/>
-    <x:col min="61" max="61" width="40" customWidth="1"/>
-    <x:col min="62" max="62" width="23" customWidth="1"/>
-    <x:col min="63" max="63" width="14" customWidth="1"/>
-    <x:col min="64" max="64" width="21" customWidth="1"/>
-    <x:col min="65" max="65" width="12" customWidth="1"/>
-    <x:col min="66" max="66" width="19" customWidth="1"/>
-    <x:col min="67" max="67" width="20" customWidth="1"/>
-    <x:col min="68" max="68" width="23" customWidth="1"/>
-    <x:col min="69" max="69" width="20.125" customWidth="1"/>
-    <x:col min="70" max="70" width="14" customWidth="1"/>
-    <x:col min="71" max="71" width="22" customWidth="1"/>
-    <x:col min="72" max="72" width="27" customWidth="1"/>
-    <x:col min="73" max="73" width="32" customWidth="1"/>
-    <x:col min="74" max="74" width="29" customWidth="1"/>
-    <x:col min="75" max="75" width="19" customWidth="1"/>
-    <x:col min="76" max="76" width="11" customWidth="1"/>
-    <x:col min="77" max="77" width="19" customWidth="1"/>
-    <x:col min="78" max="78" width="24" customWidth="1"/>
-    <x:col min="79" max="79" width="29" customWidth="1"/>
-    <x:col min="80" max="80" width="15" customWidth="1"/>
-    <x:col min="81" max="82" width="16" customWidth="1"/>
-    <x:col min="83" max="83" width="40" customWidth="1"/>
-    <x:col min="84" max="85" width="21" customWidth="1"/>
-    <x:col min="86" max="86" width="22" customWidth="1"/>
-    <x:col min="87" max="88" width="40" customWidth="1"/>
-    <x:col min="89" max="90" width="16" customWidth="1"/>
-    <x:col min="91" max="92" width="19" customWidth="1"/>
-    <x:col min="93" max="96" width="18" customWidth="1"/>
-    <x:col min="97" max="98" width="16" customWidth="1"/>
+    <x:col min="1" max="1" width="8.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.5" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="6.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="9.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="3.5" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18.25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="22.25" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="15.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="7.25" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="4.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="7.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="10" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="5.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="9.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="5.5" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="7.25" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="5.75" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="14.5" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="13.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="15.75" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="16.75" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="50" max="50" width="13" hidden="0" customWidth="1"/>
+    <x:col min="52" max="52" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="53" max="53" width="17.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="57" max="57" width="19.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="59" max="59" width="20.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="60" max="60" width="25.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="61" max="61" width="22.75" hidden="0" customWidth="1"/>
+    <x:col min="62" max="62" width="26.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="63" max="63" width="17.75" hidden="0" customWidth="1"/>
+    <x:col min="64" max="64" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="65" max="65" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="66" max="66" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="67" max="67" width="14.5" hidden="0" customWidth="1"/>
+    <x:col min="68" max="68" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="69" max="69" width="16.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="70" max="70" width="8" hidden="0" customWidth="1"/>
+    <x:col min="71" max="71" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="72" max="72" width="17.25" hidden="0" customWidth="1"/>
+    <x:col min="73" max="73" width="22.75" hidden="0" customWidth="1"/>
+    <x:col min="74" max="74" width="27" hidden="0" customWidth="1"/>
+    <x:col min="75" max="75" width="23.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="76" max="76" width="14.25" hidden="0" customWidth="1"/>
+    <x:col min="77" max="77" width="8" hidden="0" customWidth="1"/>
+    <x:col min="78" max="78" width="14.5" hidden="0" customWidth="1"/>
+    <x:col min="79" max="79" width="17.25" hidden="0" customWidth="1"/>
+    <x:col min="80" max="80" width="23.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="81" max="81" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="83" max="83" width="13.25" hidden="0" customWidth="1"/>
+    <x:col min="84" max="84" width="40.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="86" max="86" width="23.5" hidden="0" customWidth="1"/>
+    <x:col min="87" max="87" width="24" hidden="0" customWidth="1"/>
+    <x:col min="89" max="89" width="30.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="91" max="91" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="93" max="93" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="97" max="97" width="15.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="5" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="5" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="7" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="6.25" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="5.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="5" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="4.75" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="5.25" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="5" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="7" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="51" max="51" width="12.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="54" max="54" width="17.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="55" max="55" width="17.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="56" max="56" width="17.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="58" max="58" width="17.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="82" max="82" width="13" hidden="0" customWidth="1"/>
+    <x:col min="85" max="85" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="88" max="88" width="66.75" hidden="0" customWidth="1"/>
+    <x:col min="90" max="90" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="92" max="92" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="94" max="94" width="12.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="95" max="95" width="13.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="96" max="96" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="98" max="98" width="12.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="99" max="99" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="100" max="100" width="21.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -18785,6 +18834,9 @@
       </x:c>
       <x:c r="CU1" t="str">
         <x:v>walk_up_frames</x:v>
+      </x:c>
+      <x:c r="CV1" s="15" t="str">
+        <x:v>dialogue_set_id</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -19041,6 +19093,7 @@
       <x:c r="CS2"/>
       <x:c r="CT2"/>
       <x:c r="CU2"/>
+      <x:c r="CV2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -19280,6 +19333,7 @@
       <x:c r="CS3"/>
       <x:c r="CT3"/>
       <x:c r="CU3"/>
+      <x:c r="CV3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="str">
@@ -19517,6 +19571,9 @@
       <x:c r="CS4" s="7"/>
       <x:c r="CT4" s="7"/>
       <x:c r="CU4" s="7"/>
+      <x:c r="CV4" t="str">
+        <x:v>test_helper_villager_default</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24383,6 +24440,184 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="27.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>text_key</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>ja</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>item.test_iron_ore.name</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>鉄鉱石</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Iron Ore</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Step 6 regression item name</x:v>
+      </x:c>
+      <x:c r="E2" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>item.test_iron_ore.desc</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>鍛冶に使う確認用の鉱石。</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Test ore used for smithing checks.</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Step 6 regression item desc</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>npc.test_helper_villager.name</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>確認村人</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Test Villager</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Step 6 regression NPC name</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>quest.test_iron_ore_delivery.title</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>鉄鉱石の確認依頼</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Iron Ore Check Request</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Step 6 regression quest title</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>dialogue.test_helper_villager.greeting.1</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>TSV追加確認用の村人です。</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>This is a villager used for TSV checks.</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Step 7-B dialogue line</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>dialogue.test_helper_villager.greeting.2</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>今日はデータ確認日和ですね。</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>It's a good day for checking data.</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Step 7-B dialogue line</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="41.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>dialogue_set_id</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>usage</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>test_helper_villager_default</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>npc_talk</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Step 7-B regression dialogue set for test helper villager</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
@@ -24792,6 +25027,83 @@
         <x:is>
           <x:t xml:space="preserve">AUTO</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>dialogue_set_id</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>line_id</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>context</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>text_key</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>weight</x:v>
+      </x:c>
+      <x:c r="F1" s="15" t="str">
+        <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>test_helper_villager_default</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>greeting_1</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>greeting</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>dialogue.test_helper_villager.greeting.1</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>test_helper_villager_default</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>greeting_2</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>greeting</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>dialogue.test_helper_villager.greeting.2</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -2,42 +2,42 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="R4bfa38a151b048cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="R3ba94989135c4b2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R606db453a2aa4aae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="R93e76235f8384993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R12eafa9f746e4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="R5235855476d24b9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Rbccb753bac474014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="Rce4f6c3eb6904a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="R98572167c1c34561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="Rfc2211ee866049d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="Rdda5fad7656444d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R85bfa4d6878a4771"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="R916390d3d4174e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="R245b686fb8d44037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="R30978870722e4fc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="R11b547cf96f04085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="Rdd34d305459a49d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="R1c950b459e8c4c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="R823d19a3fdcb4d97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="R031f1a8c89f54c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="Rc608c174d1f74277"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="Rafa59549fd664d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="R56e53232cd514b47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R5090fbd9e5694654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R46801cf6d9d94e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="Rc945af15fe454668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="Ra6727c5cb5fe4192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="R04234b0352714ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="Rb8459b4ef7d64910"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R6b059fc38d904847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="31" r:id="R63e896545f044eed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_levels" sheetId="32" r:id="R0a4984481eb2491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_effect_links" sheetId="33" r:id="Rd4110761ff634750"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_requirements" sheetId="34" r:id="R101744c8fbce4f39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_tables" sheetId="35" r:id="R4745769874cb4115"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_entries" sheetId="36" r:id="R9e8467781c2646e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="Rfdddf6474176433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="Rbb40cfe1c5d4410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R2275be44c59c415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="Rb078134f3b7d4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R1a8d796f3ffd4ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="R713130dcc4b1472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Rf3ea15ee9c914c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="Rfb1b903fd7d44f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="R715f264ff7d4427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="Rf90bbaed5da142e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="R7105d5fed6a84bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="Rbefd6a97800f49c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="R12f4fd1c27764177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="Re9bbfc9a662d4cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="Rd7bf0df73c414a07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="Re724f821c18044b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="R56a3109eee094107"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="R6412a7964fb4490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="R025cac5f694a4f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="Rc3efd275a65c4229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="R2cc61bb14fdd4755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="R32890cb547cf4e22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="Rec10814dadfa4dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R2d58f2e93dcd4703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R45fb2a33c5eb4dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="R2eae05b946564370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="R2d270d1455124495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="Red3cf8c4c7734b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="R8f93c6e6a0704633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R42a2a2ec88674d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="31" r:id="Re83391dfee894e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_levels" sheetId="32" r:id="R458549157e49445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_effect_links" sheetId="33" r:id="Rb310807b08714863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_requirements" sheetId="34" r:id="R599b4f3f7d714d3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_tables" sheetId="35" r:id="R91187973a4ef4ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_entries" sheetId="36" r:id="Ra612c302bd174203"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19645,6 +19645,9 @@
         <x:v>success_rate</x:v>
       </x:c>
       <x:c r="J1" s="16" t="str">
+        <x:v>exp_to_next</x:v>
+      </x:c>
+      <x:c r="K1" s="16" t="str">
         <x:v>enabled</x:v>
       </x:c>
     </x:row>
@@ -19676,7 +19679,10 @@
       <x:c r="I2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J2" s="10" t="b">
+      <x:c r="J2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -19708,7 +19714,10 @@
       <x:c r="I3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J3" s="10" t="b">
+      <x:c r="J3" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -19740,7 +19749,10 @@
       <x:c r="I4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="10" t="b">
+      <x:c r="J4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -19772,7 +19784,10 @@
       <x:c r="I5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="b">
+      <x:c r="J5" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -19804,7 +19819,10 @@
       <x:c r="I6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="10" t="b">
+      <x:c r="J6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K6" s="10" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -19836,7 +19854,10 @@
       <x:c r="I7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="b">
+      <x:c r="J7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -2,42 +2,42 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="Ra60c9858e20d4a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="Rccd2b0599832496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R3334c09043c44ce4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="R09e5168ff1934c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R77e910a61b1e442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="R6f250f1400c2476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Ra65b7871a6914f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="R6c63970a724d43fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="Re0d9cde4b62a4c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="R1d524702e5164d5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="R28b3e98ac1954ba2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R18cbf709c0ca435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="R67f77beef84847be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="R10041a147c394d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="Rc03ca630f4d84f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="R2cacb94709fb4a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="R493c89998f2c4fb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="Rf3bb366179a64ca2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="R48ceb79b1c1b4f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="R417005b96f28454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="R181391d43abb4079"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="R1e0be558afcf4847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="Rebe279479eae4131"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="Rcc96e6ce8dd04a0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R50b25cd900c64618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="Rf36c4240cdbe4934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="Raa09c7aa2c6241fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="R2369b1b5fc6a4c2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="Ra34dd59edbc14ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R4e8152be7d4848ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="31" r:id="R0865d1cd433e4d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_levels" sheetId="32" r:id="R966bd6c491734ad4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_effect_links" sheetId="33" r:id="Raf772aff014a43f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_requirements" sheetId="34" r:id="Ref58769bdb744d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_tables" sheetId="35" r:id="Rd2189c0f815d4041"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_entries" sheetId="36" r:id="R7fc016b3f4b34ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="R5772711bc64f44eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="Radeadcdf76334b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R6cfaf181a6fd40a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="Raeaa65afe32d4a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R64b62d8270e4465f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="Rfefe03e5fee94e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Rf94c3e8b6411434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="R69d815e3918d42b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="R7263b28b864641a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="Raaef749a62ea47f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="Ra86b775566fa4a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R663d319df88f49b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="Re46c0840ca664290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="R5cb666672fbe426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="Ra63188e57bc5450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="R3d3aef65f8814c72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="R632f1dde8c934dfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="R8fd4f528412e4a0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="Rf6c8b46ee1a34c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="R47dab3da07784bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="Rcfac1c46a3044391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="R3a4fd30106c54f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="R8b4e7aad76a54e2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R0be1d92819fa441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R4d1a4dda57294967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="R27e064a62dca4a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="R52085ec603e94706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="R52a59d4a42324f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="Rb63b85a27703410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R66502b9f6a4b451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="31" r:id="R841a524ad8b945db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_levels" sheetId="32" r:id="Rf0cfce68bc22499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_effect_links" sheetId="33" r:id="Rde36007c6d534069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_requirements" sheetId="34" r:id="R0684ed307599491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_tables" sheetId="35" r:id="R592e6f8f46dc42e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_entries" sheetId="36" r:id="Raa604c9aaf19445a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2874,6 +2874,9 @@
           <x:t xml:space="preserve">knife</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH2" t="str">
+        <x:v>beast_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -3286,6 +3289,9 @@
           <x:t xml:space="preserve">bow</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH3" t="str">
+        <x:v>humanoid_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -3693,6 +3699,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH4" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -4105,11 +4114,7 @@
           <x:t xml:space="preserve">bat_1_initial_inventory</x:t>
         </x:is>
       </x:c>
-      <x:c r="BI5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">apple,1,1,1.0,true</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="BI5"/>
       <x:c r="BJ5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -4527,11 +4532,7 @@
           <x:t xml:space="preserve">bat_2_initial_inventory</x:t>
         </x:is>
       </x:c>
-      <x:c r="BI6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">apple,1,12,1.0,true</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="BI6"/>
       <x:c r="BJ6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -4944,6 +4945,9 @@
           <x:t xml:space="preserve">cloth_armor</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH7" t="str">
+        <x:v>beast_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -5356,6 +5360,9 @@
           <x:t xml:space="preserve">power_ring</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH8" t="str">
+        <x:v>beast_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -5763,6 +5770,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH9" t="str">
+        <x:v>construct_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -6165,6 +6175,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH10" t="str">
+        <x:v>construct_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -6567,6 +6580,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH11" t="str">
+        <x:v>construct_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -6969,6 +6985,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH12" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -7371,6 +7390,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH13" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -7773,6 +7795,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH14" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -8175,6 +8200,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH15" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -8577,6 +8605,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH16" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -8979,6 +9010,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH17" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -9381,6 +9415,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH18" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -9783,6 +9820,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH19" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -10185,6 +10225,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH20" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -10587,6 +10630,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH21" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -10989,6 +11035,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH22" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -11391,6 +11440,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH23" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -11793,6 +11845,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH24" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ24" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -12195,6 +12250,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH25" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -12597,6 +12655,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH26" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ26" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -12999,6 +13060,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH27" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ27" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -13401,6 +13465,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH28" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ28" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -13803,6 +13870,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH29" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ29" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -14205,6 +14275,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH30" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -14607,6 +14680,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH31" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -15009,6 +15085,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH32" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ32" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -15411,6 +15490,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH33" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -15813,6 +15895,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH34" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ34" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -16215,6 +16300,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH35" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ35" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -16617,6 +16705,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH36" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ36" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -17019,6 +17110,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH37" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -17421,6 +17515,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH38" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ38" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -17823,6 +17920,9 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
+      <x:c r="BH39" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
       <x:c r="BJ39" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">true</x:t>
@@ -18005,438 +18105,274 @@
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">test_training_slime</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">訓練スライム</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FOREST</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">390</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ENEMY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SLIME</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">100.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.95</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">neutral</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">neutral</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="X40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">neutral=1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AA40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AB40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AC40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AD40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AE40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AF40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AG40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AH40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AI40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AJ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AK40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AL40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AM40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AN40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AO40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AP40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AQ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AS40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AT40" s="11" t="n"/>
-      <x:c r="AU40" s="11" t="n"/>
-      <x:c r="AV40" s="11" t="n"/>
-      <x:c r="AW40" s="11" t="n"/>
-      <x:c r="AX40" s="11" t="n"/>
-      <x:c r="AY40" s="11" t="n"/>
-      <x:c r="AZ40" s="11" t="n"/>
-      <x:c r="BA40" s="11" t="n"/>
-      <x:c r="BB40" s="11" t="n"/>
-      <x:c r="BC40" s="11" t="n"/>
-      <x:c r="BD40" s="11" t="n"/>
-      <x:c r="BE40" s="11" t="n"/>
-      <x:c r="BF40" s="11" t="n"/>
-      <x:c r="BG40" s="11" t="n"/>
-      <x:c r="BH40" s="11" t="n"/>
-      <x:c r="BI40" s="11" t="n"/>
-      <x:c r="BJ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">true</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BK40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">true</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BL40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BM40" s="11" t="n"/>
-      <x:c r="BN40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BO40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BP40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BQ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BR40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">訓練スライム</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BS40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">……</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BT40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BU40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BV40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-100</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BW40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">true</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BX40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BY40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BZ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">apple</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CA40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CB40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CC40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CD40" s="11" t="n"/>
-      <x:c r="CE40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CF40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CG40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CH40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">こちらの頼みを聞くつもりか？</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CI40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">いい度胸だ。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CJ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">賢明な判断かもしれんな。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CK40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">……</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CL40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://data/lama_animation_profile.tres</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CM40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CN40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CO40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CP40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime_right_1.png|res://assets/slime_right_2.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CQ40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CR40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime_left_1.png|res://assets/slime_left_2.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CS40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CT40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime_back_1.png|res://assets/slime_back_2.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CU40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CV40" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/slime_front_1.png|res://assets/slime_front_2.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="CW40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">test_training_slime_skills</x:t>
-        </x:is>
+      <x:c r="A40" s="11" t="str">
+        <x:v>test_training_slime</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>訓練スライム</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>TEST_ONLY</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="str">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="H40" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J40" s="11" t="str">
+        <x:v>ENEMY</x:v>
+      </x:c>
+      <x:c r="K40" s="11" t="str">
+        <x:v>SLIME</x:v>
+      </x:c>
+      <x:c r="L40" s="11" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M40" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="11" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="P40" s="11" t="str">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="Q40" s="11" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="R40" s="11" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="S40" s="11" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="T40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U40" s="11" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="V40" s="11" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="W40" s="11" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="X40" s="11" t="str">
+        <x:v>neutral=1.0</x:v>
+      </x:c>
+      <x:c r="Y40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AA40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AB40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AC40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AE40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AF40" s="11" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AG40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT40" s="11"/>
+      <x:c r="AU40" s="11"/>
+      <x:c r="AV40" s="11"/>
+      <x:c r="AW40" s="11"/>
+      <x:c r="AX40" s="11"/>
+      <x:c r="AY40" s="11"/>
+      <x:c r="AZ40" s="11"/>
+      <x:c r="BA40" s="11"/>
+      <x:c r="BB40" s="11"/>
+      <x:c r="BC40" s="11"/>
+      <x:c r="BD40" s="11"/>
+      <x:c r="BE40" s="11"/>
+      <x:c r="BF40" s="11"/>
+      <x:c r="BG40" s="11"/>
+      <x:c r="BH40" s="11" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="BI40" s="11"/>
+      <x:c r="BJ40" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BK40" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BL40" s="11" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BM40" s="11"/>
+      <x:c r="BN40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="BO40" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="BQ40" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR40" s="11" t="str">
+        <x:v>訓練スライム</x:v>
+      </x:c>
+      <x:c r="BS40" s="11" t="str">
+        <x:v>……</x:v>
+      </x:c>
+      <x:c r="BT40" s="11" t="str">
+        <x:v>res://assets/slime.png</x:v>
+      </x:c>
+      <x:c r="BU40" s="11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BV40" s="11" t="str">
+        <x:v>-100</x:v>
+      </x:c>
+      <x:c r="BW40" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BX40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="BY40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="BZ40" s="11" t="str">
+        <x:v>apple</x:v>
+      </x:c>
+      <x:c r="CA40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="CB40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="CC40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="CD40" s="11"/>
+      <x:c r="CE40" s="11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="CF40" s="11" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CG40" s="11" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="CH40" s="11" t="str">
+        <x:v>こちらの頼みを聞くつもりか？</x:v>
+      </x:c>
+      <x:c r="CI40" s="11" t="str">
+        <x:v>いい度胸だ。</x:v>
+      </x:c>
+      <x:c r="CJ40" s="11" t="str">
+        <x:v>賢明な判断かもしれんな。</x:v>
+      </x:c>
+      <x:c r="CK40" s="11" t="str">
+        <x:v>……</x:v>
+      </x:c>
+      <x:c r="CL40" s="11" t="str">
+        <x:v>res://data/lama_animation_profile.tres</x:v>
+      </x:c>
+      <x:c r="CM40" s="11" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CN40" s="11" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CO40" s="11" t="str">
+        <x:v>res://assets/slime.png</x:v>
+      </x:c>
+      <x:c r="CP40" s="11" t="str">
+        <x:v>res://assets/slime_right_1.png|res://assets/slime_right_2.png</x:v>
+      </x:c>
+      <x:c r="CQ40" s="11" t="str">
+        <x:v>res://assets/slime.png</x:v>
+      </x:c>
+      <x:c r="CR40" s="11" t="str">
+        <x:v>res://assets/slime_left_1.png|res://assets/slime_left_2.png</x:v>
+      </x:c>
+      <x:c r="CS40" s="11" t="str">
+        <x:v>res://assets/slime.png</x:v>
+      </x:c>
+      <x:c r="CT40" s="11" t="str">
+        <x:v>res://assets/slime_back_1.png|res://assets/slime_back_2.png</x:v>
+      </x:c>
+      <x:c r="CU40" s="11" t="str">
+        <x:v>res://assets/slime.png</x:v>
+      </x:c>
+      <x:c r="CV40" s="11" t="str">
+        <x:v>res://assets/slime_front_1.png|res://assets/slime_front_2.png</x:v>
+      </x:c>
+      <x:c r="CW40" t="str">
+        <x:v>test_training_slime_skills</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22956,13 +22892,13 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>sample_flame_knife</x:v>
+        <x:v>sample_poison_knife</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>火花のナイフ</x:v>
+        <x:v>毒牙のナイフ</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>攻撃命中時に追加 fire direct damage 1 が発動するサンプルナイフ。</x:v>
+        <x:v>攻撃命中時に poison を付与するサンプルナイフ。</x:v>
       </x:c>
       <x:c r="D43" t="str">
         <x:v>equipment</x:v>
@@ -22997,13 +22933,13 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>sample_poison_knife</x:v>
+        <x:v>sample_dud_flame_knife</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>毒牙のナイフ</x:v>
+        <x:v>不発の火花ナイフ</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>攻撃命中時に poison を付与するサンプルナイフ。</x:v>
+        <x:v>trigger_chance=0.0 で常に proc_failed になるサンプルナイフ。</x:v>
       </x:c>
       <x:c r="D44" t="str">
         <x:v>equipment</x:v>
@@ -23038,13 +22974,13 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>sample_drain_knife</x:v>
+        <x:v>sample_unstable_flame_knife</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>吸命のナイフ</x:v>
+        <x:v>揺らめき火のナイフ</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>攻撃命中時に attacker の HP を1回復するサンプルナイフ。</x:v>
+        <x:v>trigger_chance=0.5 で攻撃時効果が半分程度発動するサンプルナイフ。</x:v>
       </x:c>
       <x:c r="D45" t="str">
         <x:v>equipment</x:v>
@@ -23079,13 +23015,13 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>sample_dud_flame_knife</x:v>
+        <x:v>sample_combo_knife</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>不発の火花ナイフ</x:v>
+        <x:v>複合効果のナイフ</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>trigger_chance=0.0 で常に proc_failed になるサンプルナイフ。</x:v>
+        <x:v>攻撃命中時に追加ダメージとHP回復を同時に確認するサンプルナイフ。</x:v>
       </x:c>
       <x:c r="D46" t="str">
         <x:v>equipment</x:v>
@@ -23093,112 +23029,60 @@
       <x:c r="E46" t="str">
         <x:v>res://assets/items/knife.png</x:v>
       </x:c>
-      <x:c r="F46" t="n">
+      <x:c r="F46" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G46" s="18" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H46" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I46" s="18" t="b">
+      <x:c r="G46" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J46" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M46" t="n">
+      <x:c r="K46" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" t="str">
-        <x:v>sample_unstable_flame_knife</x:v>
-      </x:c>
-      <x:c r="B47" t="str">
-        <x:v>揺らめき火のナイフ</x:v>
-      </x:c>
-      <x:c r="C47" t="str">
-        <x:v>trigger_chance=0.5 で攻撃時効果が半分程度発動するサンプルナイフ。</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
-        <x:v>equipment</x:v>
-      </x:c>
-      <x:c r="E47" t="str">
-        <x:v>res://assets/items/knife.png</x:v>
-      </x:c>
-      <x:c r="F47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G47" s="18" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H47" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I47" s="18" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K47" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L47" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M47" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47"/>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47"/>
+      <x:c r="L47"/>
+      <x:c r="M47"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" t="str">
-        <x:v>sample_combo_knife</x:v>
-      </x:c>
-      <x:c r="B48" t="str">
-        <x:v>複合効果のナイフ</x:v>
-      </x:c>
-      <x:c r="C48" t="str">
-        <x:v>攻撃命中時に追加ダメージとHP回復を同時に確認するサンプルナイフ。</x:v>
-      </x:c>
-      <x:c r="D48" t="str">
-        <x:v>equipment</x:v>
-      </x:c>
-      <x:c r="E48" t="str">
-        <x:v>res://assets/items/knife.png</x:v>
-      </x:c>
-      <x:c r="F48" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G48" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="H48" t="str">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I48" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="J48" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K48" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L48" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M48" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A48"/>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+      <x:c r="G48"/>
+      <x:c r="H48"/>
+      <x:c r="I48"/>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
+      <x:c r="M48"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23867,6 +23751,83 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>訓練用スライム所持品</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>訓練用・確認用スライムが持つ軽い食料と素材の確認用テーブル。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Weak enemy basic inventory</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Small common item rolls for low-tier normal enemies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>beast_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Beast basic inventory</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Food item rolls for beast or wildlife enemies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>humanoid_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Humanoid basic inventory</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Small gold and consumable rolls for humanoid enemies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Plant basic inventory</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Low chance material and food rolls for plant-type normal enemies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Undead basic inventory</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Low chance gold and eerie consumable rolls for undead normal enemies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>construct_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Construct basic inventory</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Low chance small item rolls for block or construct-like normal enemies.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -23897,10 +23858,8 @@
           <x:t xml:space="preserve">max_amount</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">drop_chance</x:t>
-        </x:is>
+      <x:c r="E1" t="str">
+        <x:v>spawn_chance</x:v>
       </x:c>
       <x:c r="F1" t="inlineStr">
         <x:is>
@@ -23985,6 +23944,489 @@
         <x:is>
           <x:t xml:space="preserve">true</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>apple</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>bread</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>0.40</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>mushroom_bad</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>0.10</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>test_random_inventory</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>wood</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>0.10</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>apple</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F9" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>bread</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>weak_enemy_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>beast_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>apple</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>beast_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>meat_skewer</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>humanoid_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>humanoid_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>bread</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>humanoid_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>healing_potion</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>wood</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>apple</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>plant_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>mushroom_bad</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="C20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>hallucination_powder</x:v>
+      </x:c>
+      <x:c r="C21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>undead_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>curse_orb</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>construct_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>construct_basic_inventory</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>wood</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -24861,7 +25303,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>sample_flame_knife</x:v>
+        <x:v>sample_poison_knife</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>HAND</x:v>
@@ -24870,7 +25312,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>0</x:v>
@@ -24902,7 +25344,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>sample_poison_knife</x:v>
+        <x:v>sample_dud_flame_knife</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>HAND</x:v>
@@ -24943,7 +25385,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>sample_drain_knife</x:v>
+        <x:v>sample_unstable_flame_knife</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>HAND</x:v>
@@ -24984,21 +25426,21 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>sample_dud_flame_knife</x:v>
+        <x:v>sample_combo_knife</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>HAND</x:v>
       </x:c>
-      <x:c r="C10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
+      <x:c r="C10" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
+      <x:c r="E10" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G10" t="str">
@@ -25010,10 +25452,10 @@
       <x:c r="I10" t="str">
         <x:v>physical</x:v>
       </x:c>
-      <x:c r="J10" t="n">
+      <x:c r="J10" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" t="n">
+      <x:c r="K10" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L10" t="str">
@@ -25024,86 +25466,34 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>sample_unstable_flame_knife</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>HAND</x:v>
-      </x:c>
-      <x:c r="C11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>neutral</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>physical</x:v>
-      </x:c>
-      <x:c r="J11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L11" t="str">
-        <x:v>MELEE</x:v>
-      </x:c>
-      <x:c r="M11" t="str">
-        <x:v>APPROACH</x:v>
-      </x:c>
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>sample_combo_knife</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>HAND</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>neutral</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>physical</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L12" t="str">
-        <x:v>MELEE</x:v>
-      </x:c>
-      <x:c r="M12" t="str">
-        <x:v>APPROACH</x:v>
-      </x:c>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+      <x:c r="M12"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29332,26 +29722,26 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>sample_flame_knife_fire_damage</x:v>
+        <x:v>sample_poison_knife_poison</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>deal_damage</x:v>
+        <x:v>apply_status</x:v>
       </x:c>
       <x:c r="C36" t="str">
         <x:v>flat</x:v>
       </x:c>
       <x:c r="D36"/>
       <x:c r="E36" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" t="str">
-        <x:v>fire</x:v>
+        <x:v>neutral</x:v>
       </x:c>
       <x:c r="I36" t="str">
         <x:v>physical</x:v>
@@ -29374,9 +29764,11 @@
       <x:c r="O36" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P36"/>
+      <x:c r="P36" t="str">
+        <x:v>poison</x:v>
+      </x:c>
       <x:c r="Q36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R36"/>
       <x:c r="S36"/>
@@ -29387,10 +29779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="V36" t="str">
-        <x:v>none</x:v>
+        <x:v>time</x:v>
       </x:c>
       <x:c r="W36" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X36" t="str">
         <x:v>random</x:v>
@@ -29422,26 +29814,26 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>sample_poison_knife_poison</x:v>
+        <x:v>sample_dud_flame_knife_fire_damage</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>apply_status</x:v>
+        <x:v>deal_damage</x:v>
       </x:c>
       <x:c r="C37" t="str">
         <x:v>flat</x:v>
       </x:c>
       <x:c r="D37"/>
       <x:c r="E37" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" t="str">
-        <x:v>neutral</x:v>
+        <x:v>fire</x:v>
       </x:c>
       <x:c r="I37" t="str">
         <x:v>physical</x:v>
@@ -29464,11 +29856,9 @@
       <x:c r="O37" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P37" t="str">
-        <x:v>poison</x:v>
-      </x:c>
+      <x:c r="P37"/>
       <x:c r="Q37" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R37"/>
       <x:c r="S37"/>
@@ -29479,10 +29869,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="V37" t="str">
-        <x:v>time</x:v>
+        <x:v>none</x:v>
       </x:c>
       <x:c r="W37" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X37" t="str">
         <x:v>random</x:v>
@@ -29510,21 +29900,21 @@
       <x:c r="AI37"/>
       <x:c r="AJ37"/>
       <x:c r="AK37"/>
-      <x:c r="AL37"/>
+      <x:c r="AL37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>sample_drain_knife_restore_hp</x:v>
+        <x:v>sample_unstable_flame_knife_fire_damage</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>restore_resource</x:v>
+        <x:v>deal_damage</x:v>
       </x:c>
       <x:c r="C38" t="str">
         <x:v>flat</x:v>
       </x:c>
-      <x:c r="D38" t="str">
-        <x:v>hp</x:v>
-      </x:c>
+      <x:c r="D38"/>
       <x:c r="E38" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -29535,7 +29925,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" t="str">
-        <x:v>neutral</x:v>
+        <x:v>fire</x:v>
       </x:c>
       <x:c r="I38" t="str">
         <x:v>physical</x:v>
@@ -29602,30 +29992,32 @@
       <x:c r="AI38"/>
       <x:c r="AJ38"/>
       <x:c r="AK38"/>
-      <x:c r="AL38"/>
+      <x:c r="AL38" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>sample_dud_flame_knife_fire_damage</x:v>
+        <x:v>power_ring_attack_bonus</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>deal_damage</x:v>
+        <x:v>apply_modifier</x:v>
       </x:c>
       <x:c r="C39" t="str">
         <x:v>flat</x:v>
       </x:c>
       <x:c r="D39"/>
-      <x:c r="E39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G39" t="n">
+      <x:c r="E39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" t="str">
-        <x:v>fire</x:v>
+        <x:v>neutral</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>physical</x:v>
@@ -29633,72 +30025,74 @@
       <x:c r="J39" t="str">
         <x:v>direct</x:v>
       </x:c>
-      <x:c r="K39" t="n">
+      <x:c r="K39" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O39" t="n">
+      <x:c r="L39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P39"/>
-      <x:c r="Q39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R39"/>
-      <x:c r="S39"/>
-      <x:c r="T39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U39" t="n">
+      <x:c r="Q39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="V39" t="str">
         <x:v>none</x:v>
       </x:c>
-      <x:c r="W39" t="n">
+      <x:c r="W39" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="X39" t="str">
         <x:v>random</x:v>
       </x:c>
-      <x:c r="Y39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z39" t="n">
+      <x:c r="Y39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z39" t="str">
         <x:v>999</x:v>
       </x:c>
       <x:c r="AA39"/>
       <x:c r="AB39"/>
-      <x:c r="AC39" t="n">
+      <x:c r="AC39" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AD39" t="n">
+      <x:c r="AD39" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE39"/>
       <x:c r="AF39"/>
-      <x:c r="AG39" s="18" t="b">
-        <x:v>0</x:v>
+      <x:c r="AG39" t="str">
+        <x:v>false</x:v>
       </x:c>
       <x:c r="AH39"/>
       <x:c r="AI39"/>
       <x:c r="AJ39"/>
       <x:c r="AK39"/>
-      <x:c r="AL39" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="AL39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>sample_unstable_flame_knife_fire_damage</x:v>
+        <x:v>sample_combo_knife_fire_damage</x:v>
       </x:c>
       <x:c r="B40" t="str">
         <x:v>deal_damage</x:v>
@@ -29707,13 +30101,13 @@
         <x:v>flat</x:v>
       </x:c>
       <x:c r="D40"/>
-      <x:c r="E40" t="n">
+      <x:c r="E40" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F40" t="n">
+      <x:c r="F40" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G40" t="n">
+      <x:c r="G40" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H40" t="str">
@@ -29725,85 +30119,85 @@
       <x:c r="J40" t="str">
         <x:v>direct</x:v>
       </x:c>
-      <x:c r="K40" t="n">
+      <x:c r="K40" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O40" t="n">
+      <x:c r="L40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P40"/>
-      <x:c r="Q40" t="n">
+      <x:c r="Q40" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R40"/>
       <x:c r="S40"/>
-      <x:c r="T40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U40" t="n">
+      <x:c r="T40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="V40" t="str">
         <x:v>none</x:v>
       </x:c>
-      <x:c r="W40" t="n">
+      <x:c r="W40" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="X40" t="str">
         <x:v>random</x:v>
       </x:c>
-      <x:c r="Y40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z40" t="n">
+      <x:c r="Y40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z40" t="str">
         <x:v>999</x:v>
       </x:c>
       <x:c r="AA40"/>
       <x:c r="AB40"/>
-      <x:c r="AC40" t="n">
+      <x:c r="AC40" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AD40" t="n">
+      <x:c r="AD40" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE40"/>
       <x:c r="AF40"/>
-      <x:c r="AG40" s="18" t="b">
-        <x:v>0</x:v>
+      <x:c r="AG40" t="str">
+        <x:v>false</x:v>
       </x:c>
       <x:c r="AH40"/>
       <x:c r="AI40"/>
       <x:c r="AJ40"/>
       <x:c r="AK40"/>
-      <x:c r="AL40" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="AL40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>power_ring_attack_bonus</x:v>
+        <x:v>sample_combo_knife_restore_hp</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>apply_modifier</x:v>
+        <x:v>restore_resource</x:v>
       </x:c>
       <x:c r="C41" t="str">
         <x:v>flat</x:v>
       </x:c>
-      <x:c r="D41"/>
+      <x:c r="D41" t="str">
+        <x:v>hp</x:v>
+      </x:c>
       <x:c r="E41" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F41" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G41" t="str">
         <x:v>0</x:v>
@@ -29836,14 +30230,10 @@
       <x:c r="Q41" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R41" t="str">
-        <x:v>buff</x:v>
-      </x:c>
-      <x:c r="S41" t="str">
-        <x:v>attack</x:v>
-      </x:c>
+      <x:c r="R41"/>
+      <x:c r="S41"/>
       <x:c r="T41" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U41" t="str">
         <x:v>0</x:v>
@@ -29883,89 +30273,39 @@
       <x:c r="AL41"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="str">
-        <x:v>sample_combo_knife_fire_damage</x:v>
-      </x:c>
-      <x:c r="B42" t="str">
-        <x:v>deal_damage</x:v>
-      </x:c>
-      <x:c r="C42" t="str">
-        <x:v>flat</x:v>
-      </x:c>
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
       <x:c r="D42"/>
-      <x:c r="E42" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F42" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" t="str">
-        <x:v>fire</x:v>
-      </x:c>
-      <x:c r="I42" t="str">
-        <x:v>physical</x:v>
-      </x:c>
-      <x:c r="J42" t="str">
-        <x:v>direct</x:v>
-      </x:c>
-      <x:c r="K42" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O42" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
+      <x:c r="G42"/>
+      <x:c r="H42"/>
+      <x:c r="I42"/>
+      <x:c r="J42"/>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
+      <x:c r="M42"/>
+      <x:c r="N42"/>
+      <x:c r="O42"/>
       <x:c r="P42"/>
-      <x:c r="Q42" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="Q42"/>
       <x:c r="R42"/>
       <x:c r="S42"/>
-      <x:c r="T42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V42" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="W42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X42" t="str">
-        <x:v>random</x:v>
-      </x:c>
-      <x:c r="Y42" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z42" t="str">
-        <x:v>999</x:v>
-      </x:c>
+      <x:c r="T42"/>
+      <x:c r="U42"/>
+      <x:c r="V42"/>
+      <x:c r="W42"/>
+      <x:c r="X42"/>
+      <x:c r="Y42"/>
+      <x:c r="Z42"/>
       <x:c r="AA42"/>
       <x:c r="AB42"/>
-      <x:c r="AC42" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD42" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="AC42"/>
+      <x:c r="AD42"/>
       <x:c r="AE42"/>
       <x:c r="AF42"/>
-      <x:c r="AG42" t="str">
-        <x:v>false</x:v>
-      </x:c>
+      <x:c r="AG42"/>
       <x:c r="AH42"/>
       <x:c r="AI42"/>
       <x:c r="AJ42"/>
@@ -29973,91 +30313,39 @@
       <x:c r="AL42"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" t="str">
-        <x:v>sample_combo_knife_restore_hp</x:v>
-      </x:c>
-      <x:c r="B43" t="str">
-        <x:v>restore_resource</x:v>
-      </x:c>
-      <x:c r="C43" t="str">
-        <x:v>flat</x:v>
-      </x:c>
-      <x:c r="D43" t="str">
-        <x:v>hp</x:v>
-      </x:c>
-      <x:c r="E43" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F43" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" t="str">
-        <x:v>neutral</x:v>
-      </x:c>
-      <x:c r="I43" t="str">
-        <x:v>physical</x:v>
-      </x:c>
-      <x:c r="J43" t="str">
-        <x:v>direct</x:v>
-      </x:c>
-      <x:c r="K43" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O43" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A43"/>
+      <x:c r="B43"/>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43"/>
+      <x:c r="G43"/>
+      <x:c r="H43"/>
+      <x:c r="I43"/>
+      <x:c r="J43"/>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
+      <x:c r="M43"/>
+      <x:c r="N43"/>
+      <x:c r="O43"/>
       <x:c r="P43"/>
-      <x:c r="Q43" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="Q43"/>
       <x:c r="R43"/>
       <x:c r="S43"/>
-      <x:c r="T43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V43" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="W43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X43" t="str">
-        <x:v>random</x:v>
-      </x:c>
-      <x:c r="Y43" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z43" t="str">
-        <x:v>999</x:v>
-      </x:c>
+      <x:c r="T43"/>
+      <x:c r="U43"/>
+      <x:c r="V43"/>
+      <x:c r="W43"/>
+      <x:c r="X43"/>
+      <x:c r="Y43"/>
+      <x:c r="Z43"/>
       <x:c r="AA43"/>
       <x:c r="AB43"/>
-      <x:c r="AC43" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD43" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="AC43"/>
+      <x:c r="AD43"/>
       <x:c r="AE43"/>
       <x:c r="AF43"/>
-      <x:c r="AG43" t="str">
-        <x:v>false</x:v>
-      </x:c>
+      <x:c r="AG43"/>
       <x:c r="AH43"/>
       <x:c r="AI43"/>
       <x:c r="AJ43"/>
@@ -30463,10 +30751,10 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>sample_flame_knife</x:v>
+        <x:v>sample_poison_knife</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>sample_flame_knife_fire_damage</x:v>
+        <x:v>sample_poison_knife_poison</x:v>
       </x:c>
       <x:c r="C36" t="n">
         <x:v>1</x:v>
@@ -30474,10 +30762,10 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>sample_poison_knife</x:v>
+        <x:v>sample_dud_flame_knife</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>sample_poison_knife_poison</x:v>
+        <x:v>sample_dud_flame_knife_fire_damage</x:v>
       </x:c>
       <x:c r="C37" t="n">
         <x:v>1</x:v>
@@ -30485,10 +30773,10 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>sample_drain_knife</x:v>
+        <x:v>sample_unstable_flame_knife</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>sample_drain_knife_restore_hp</x:v>
+        <x:v>sample_unstable_flame_knife_fire_damage</x:v>
       </x:c>
       <x:c r="C38" t="n">
         <x:v>1</x:v>
@@ -30496,58 +30784,46 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>sample_dud_flame_knife</x:v>
+        <x:v>power_ring</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>sample_dud_flame_knife_fire_damage</x:v>
-      </x:c>
-      <x:c r="C39" t="n">
+        <x:v>power_ring_attack_bonus</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>sample_unstable_flame_knife</x:v>
+        <x:v>sample_combo_knife</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>sample_unstable_flame_knife_fire_damage</x:v>
-      </x:c>
-      <x:c r="C40" t="n">
+        <x:v>sample_combo_knife_fire_damage</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>power_ring</x:v>
+        <x:v>sample_combo_knife</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>power_ring_attack_bonus</x:v>
+        <x:v>sample_combo_knife_restore_hp</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="str">
-        <x:v>sample_combo_knife</x:v>
-      </x:c>
-      <x:c r="B42" t="str">
-        <x:v>sample_combo_knife_fire_damage</x:v>
-      </x:c>
-      <x:c r="C42" t="str">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" t="str">
-        <x:v>sample_combo_knife</x:v>
-      </x:c>
-      <x:c r="B43" t="str">
-        <x:v>sample_combo_knife_restore_hp</x:v>
-      </x:c>
-      <x:c r="C43" t="str">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A43"/>
+      <x:c r="B43"/>
+      <x:c r="C43"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -2,42 +2,42 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="R5772711bc64f44eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="Radeadcdf76334b80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R6cfaf181a6fd40a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="Raeaa65afe32d4a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R64b62d8270e4465f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="Rfefe03e5fee94e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Rf94c3e8b6411434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="R69d815e3918d42b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="R7263b28b864641a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="Raaef749a62ea47f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="Ra86b775566fa4a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R663d319df88f49b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="Re46c0840ca664290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="R5cb666672fbe426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="Ra63188e57bc5450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="R3d3aef65f8814c72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="R632f1dde8c934dfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="R8fd4f528412e4a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="Rf6c8b46ee1a34c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="R47dab3da07784bb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="Rcfac1c46a3044391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="R3a4fd30106c54f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="R8b4e7aad76a54e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R0be1d92819fa441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R4d1a4dda57294967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="R27e064a62dca4a0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="R52085ec603e94706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="R52a59d4a42324f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="Rb63b85a27703410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R66502b9f6a4b451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="31" r:id="R841a524ad8b945db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_levels" sheetId="32" r:id="Rf0cfce68bc22499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_effect_links" sheetId="33" r:id="Rde36007c6d534069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_requirements" sheetId="34" r:id="R0684ed307599491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_tables" sheetId="35" r:id="R592e6f8f46dc42e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_entries" sheetId="36" r:id="Raa604c9aaf19445a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="1" r:id="R52d40fb0931c47f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" r:id="R9a67bbe025124f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="3" r:id="R6857f91e129a4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effects" sheetId="4" r:id="R8b574a3ff33f478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_effect_links" sheetId="5" r:id="R8c123018fd3a4e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_tables" sheetId="6" r:id="R07f49bc944624efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chest_loot_tables" sheetId="7" r:id="Rcd8b8884cc7b496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_tables" sheetId="8" r:id="R626e3b03a16f449f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_loot_tables" sheetId="9" r:id="Rd9a14437a5784c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_races" sheetId="10" r:id="R959553ec2d2b488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quests" sheetId="11" r:id="Ra470949746204088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rules" sheetId="12" r:id="R504e257306864fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemies" sheetId="13" r:id="R306b6e36e502439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npcs" sheetId="14" r:id="R184673d649fb4aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enchantments" sheetId="15" r:id="Rc065801702af4277"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dungeon_spawn_rules" sheetId="16" r:id="R390d8a1278ee4a52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_spawn_rules" sheetId="17" r:id="R14686200d35a4938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="18" r:id="R65070825e4214ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faction_relations" sheetId="19" r:id="Rf527c30d6f844802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="element_types" sheetId="20" r:id="R23cc47226eb84d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="damage_types" sheetId="21" r:id="R952266b117f34686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status_effect_types" sheetId="22" r:id="R6fb5206d11e34cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_tables" sheetId="23" r:id="R42fc3fc2dc1a43d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial_inventory_entries" sheetId="24" r:id="R858f48a27acf473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spawn_rule_category_multipliers" sheetId="25" r:id="R08ee3d4aafd147fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_spawn_rule_item_overrides" sheetId="26" r:id="Ra43d4ab4fe784653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_quest_links" sheetId="27" r:id="R91a3c464556c47f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="localization_texts" sheetId="28" r:id="R81919268ecd2420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_sets" sheetId="29" r:id="Re4656e0ca53848c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue_lines" sheetId="30" r:id="R2a5c1f6cd6aa4a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="31" r:id="R0eecd53d720345bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_levels" sheetId="32" r:id="R893d72be39b24dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_effect_links" sheetId="33" r:id="Ra89d998cee974649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_requirements" sheetId="34" r:id="R1e0baab485004e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_tables" sheetId="35" r:id="R7c3c558fdbfc4406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_skill_entries" sheetId="36" r:id="R70265f6c2b74408c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23055,34 +23055,414 @@
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47"/>
-      <x:c r="B47"/>
-      <x:c r="C47"/>
-      <x:c r="D47"/>
-      <x:c r="E47"/>
-      <x:c r="F47"/>
-      <x:c r="G47"/>
-      <x:c r="H47"/>
-      <x:c r="I47"/>
-      <x:c r="J47"/>
-      <x:c r="K47"/>
-      <x:c r="L47"/>
-      <x:c r="M47"/>
+      <x:c r="A47" t="str">
+        <x:v>medicinal_herb</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>薬草</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>HPを少量回復する一般的な薬草。自分で使うことも、対象へ投げて使うこともできる。</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G47" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I47" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M47" t="n">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48"/>
-      <x:c r="B48"/>
-      <x:c r="C48"/>
-      <x:c r="D48"/>
-      <x:c r="E48"/>
-      <x:c r="F48"/>
-      <x:c r="G48"/>
-      <x:c r="H48"/>
-      <x:c r="I48"/>
-      <x:c r="J48"/>
-      <x:c r="K48"/>
-      <x:c r="L48"/>
-      <x:c r="M48"/>
+      <x:c r="A48" t="str">
+        <x:v>high_healing_potion</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>上級回復ポーション</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>HPを大きく回復する高品質なポーション。自分で飲むことも、対象へ投げて使うこともできる。</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G48" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I48" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J48" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K48" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="L48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M48" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>wakeup_potion</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>目覚まし薬</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>睡眠状態を解除する刺激の強い薬。</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G49" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H49" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I49" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J49" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K49" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>clarity_potion</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>正気の薬</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>混乱状態を解除し、意識をはっきりさせる薬。</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F50" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G50" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H50" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="I50" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J50" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K50" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>burn_salve</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>火傷軟膏</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>炎上状態を解除する冷却効果のある軟膏。</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F51" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G51" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H51" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I51" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K51" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>frost_remedy</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>凍傷治療薬</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>凍傷状態を解除し、冷えた身体を温める薬。</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>consumable</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G52" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I52" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>iron_ore</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>鉄鉱石</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>武器や防具の材料として利用できそうな鉱石。</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>material</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F53" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G53" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H53" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I53" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K53" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>monster_fang</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>魔物の牙</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>魔物から採れる鋭い牙。素材として売却できる。</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>material</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>res://assets/Tentative_Assets/item.png</x:v>
+      </x:c>
+      <x:c r="F54" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G54" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H54" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I54" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K54" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>rusty_sword</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>錆びた剣</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>全体に錆が浮いている古い剣。切れ味はあまり良くない。</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>res://assets/Tentative_Assets/hand.png</x:v>
+      </x:c>
+      <x:c r="F55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I55" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>leather_armor</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>革の鎧</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>なめした革で作られた軽くて扱いやすい鎧。</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>res://assets/Tentative_Assets/body.png</x:v>
+      </x:c>
+      <x:c r="F56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I56" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K56" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M56" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25466,34 +25846,86 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-      <x:c r="I11"/>
-      <x:c r="J11"/>
-      <x:c r="K11"/>
-      <x:c r="L11"/>
-      <x:c r="M11"/>
+      <x:c r="A11" t="str">
+        <x:v>rusty_sword</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>HAND</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L11" t="str">
+        <x:v>MELEE</x:v>
+      </x:c>
+      <x:c r="M11" t="str">
+        <x:v>APPROACH</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-      <x:c r="I12"/>
-      <x:c r="J12"/>
-      <x:c r="K12"/>
-      <x:c r="L12"/>
-      <x:c r="M12"/>
+      <x:c r="A12" t="str">
+        <x:v>leather_armor</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>BODY</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" t="str">
+        <x:v>AUTO</x:v>
+      </x:c>
+      <x:c r="M12" t="str">
+        <x:v>AUTO</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30273,39 +30705,91 @@
       <x:c r="AL41"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42"/>
-      <x:c r="B42"/>
-      <x:c r="C42"/>
-      <x:c r="D42"/>
-      <x:c r="E42"/>
-      <x:c r="F42"/>
-      <x:c r="G42"/>
-      <x:c r="H42"/>
-      <x:c r="I42"/>
-      <x:c r="J42"/>
-      <x:c r="K42"/>
-      <x:c r="L42"/>
-      <x:c r="M42"/>
-      <x:c r="N42"/>
-      <x:c r="O42"/>
+      <x:c r="A42" t="str">
+        <x:v>medicinal_herb_restore_hp</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>restore_resource</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>hp</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>direct</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O42" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="P42"/>
-      <x:c r="Q42"/>
+      <x:c r="Q42" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R42"/>
       <x:c r="S42"/>
-      <x:c r="T42"/>
-      <x:c r="U42"/>
-      <x:c r="V42"/>
-      <x:c r="W42"/>
-      <x:c r="X42"/>
-      <x:c r="Y42"/>
-      <x:c r="Z42"/>
+      <x:c r="T42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="W42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X42" t="str">
+        <x:v>random</x:v>
+      </x:c>
+      <x:c r="Y42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z42" t="n">
+        <x:v>999</x:v>
+      </x:c>
       <x:c r="AA42"/>
       <x:c r="AB42"/>
-      <x:c r="AC42"/>
-      <x:c r="AD42"/>
+      <x:c r="AC42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD42" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="AE42"/>
       <x:c r="AF42"/>
-      <x:c r="AG42"/>
+      <x:c r="AG42" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="AH42"/>
       <x:c r="AI42"/>
       <x:c r="AJ42"/>
@@ -30313,44 +30797,464 @@
       <x:c r="AL42"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43"/>
-      <x:c r="B43"/>
-      <x:c r="C43"/>
-      <x:c r="D43"/>
-      <x:c r="E43"/>
-      <x:c r="F43"/>
-      <x:c r="G43"/>
-      <x:c r="H43"/>
-      <x:c r="I43"/>
-      <x:c r="J43"/>
-      <x:c r="K43"/>
-      <x:c r="L43"/>
-      <x:c r="M43"/>
-      <x:c r="N43"/>
-      <x:c r="O43"/>
+      <x:c r="A43" t="str">
+        <x:v>high_healing_potion_restore_hp</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>restore_resource</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>hp</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>direct</x:v>
+      </x:c>
+      <x:c r="K43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="P43"/>
-      <x:c r="Q43"/>
+      <x:c r="Q43" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R43"/>
       <x:c r="S43"/>
-      <x:c r="T43"/>
-      <x:c r="U43"/>
-      <x:c r="V43"/>
-      <x:c r="W43"/>
-      <x:c r="X43"/>
-      <x:c r="Y43"/>
-      <x:c r="Z43"/>
+      <x:c r="T43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="W43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X43" t="str">
+        <x:v>random</x:v>
+      </x:c>
+      <x:c r="Y43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z43" t="n">
+        <x:v>999</x:v>
+      </x:c>
       <x:c r="AA43"/>
       <x:c r="AB43"/>
-      <x:c r="AC43"/>
-      <x:c r="AD43"/>
+      <x:c r="AC43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD43" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="AE43"/>
       <x:c r="AF43"/>
-      <x:c r="AG43"/>
+      <x:c r="AG43" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="AH43"/>
       <x:c r="AI43"/>
       <x:c r="AJ43"/>
       <x:c r="AK43"/>
       <x:c r="AL43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>wakeup_potion_cure_sleep</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>cure_status</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="D44"/>
+      <x:c r="E44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>direct</x:v>
+      </x:c>
+      <x:c r="K44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>sleep</x:v>
+      </x:c>
+      <x:c r="Q44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R44"/>
+      <x:c r="S44"/>
+      <x:c r="T44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="W44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X44" t="str">
+        <x:v>random</x:v>
+      </x:c>
+      <x:c r="Y44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z44" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="AA44"/>
+      <x:c r="AB44"/>
+      <x:c r="AC44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE44"/>
+      <x:c r="AF44"/>
+      <x:c r="AG44" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH44"/>
+      <x:c r="AI44"/>
+      <x:c r="AJ44"/>
+      <x:c r="AK44"/>
+      <x:c r="AL44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>clarity_potion_cure_confusion</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>cure_status</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="D45"/>
+      <x:c r="E45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>direct</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>confusion</x:v>
+      </x:c>
+      <x:c r="Q45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R45"/>
+      <x:c r="S45"/>
+      <x:c r="T45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="W45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X45" t="str">
+        <x:v>random</x:v>
+      </x:c>
+      <x:c r="Y45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z45" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="AA45"/>
+      <x:c r="AB45"/>
+      <x:c r="AC45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE45"/>
+      <x:c r="AF45"/>
+      <x:c r="AG45" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH45"/>
+      <x:c r="AI45"/>
+      <x:c r="AJ45"/>
+      <x:c r="AK45"/>
+      <x:c r="AL45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>burn_salve_cure_burning</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>cure_status</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="D46"/>
+      <x:c r="E46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>direct</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>burning</x:v>
+      </x:c>
+      <x:c r="Q46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R46"/>
+      <x:c r="S46"/>
+      <x:c r="T46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="W46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X46" t="str">
+        <x:v>random</x:v>
+      </x:c>
+      <x:c r="Y46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z46" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="AA46"/>
+      <x:c r="AB46"/>
+      <x:c r="AC46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE46"/>
+      <x:c r="AF46"/>
+      <x:c r="AG46" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH46"/>
+      <x:c r="AI46"/>
+      <x:c r="AJ46"/>
+      <x:c r="AK46"/>
+      <x:c r="AL46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>frost_remedy_cure_frostbite</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>cure_status</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="D47"/>
+      <x:c r="E47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>physical</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>direct</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>frostbite</x:v>
+      </x:c>
+      <x:c r="Q47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R47"/>
+      <x:c r="S47"/>
+      <x:c r="T47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="W47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X47" t="str">
+        <x:v>random</x:v>
+      </x:c>
+      <x:c r="Y47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z47" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="AA47"/>
+      <x:c r="AB47"/>
+      <x:c r="AC47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE47"/>
+      <x:c r="AF47"/>
+      <x:c r="AG47" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH47"/>
+      <x:c r="AI47"/>
+      <x:c r="AJ47"/>
+      <x:c r="AK47"/>
+      <x:c r="AL47"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30816,14 +31720,70 @@
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42"/>
-      <x:c r="B42"/>
-      <x:c r="C42"/>
+      <x:c r="A42" t="str">
+        <x:v>medicinal_herb</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>medicinal_herb_restore_hp</x:v>
+      </x:c>
+      <x:c r="C42" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43"/>
-      <x:c r="B43"/>
-      <x:c r="C43"/>
+      <x:c r="A43" t="str">
+        <x:v>high_healing_potion</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>high_healing_potion_restore_hp</x:v>
+      </x:c>
+      <x:c r="C43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>wakeup_potion</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>wakeup_potion_cure_sleep</x:v>
+      </x:c>
+      <x:c r="C44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>clarity_potion</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>clarity_potion_cure_confusion</x:v>
+      </x:c>
+      <x:c r="C45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>burn_salve</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>burn_salve_cure_burning</x:v>
+      </x:c>
+      <x:c r="C46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>frost_remedy</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>frost_remedy_cure_frostbite</x:v>
+      </x:c>
+      <x:c r="C47" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
